--- a/02-示例报表/最终排名-示例.xlsx
+++ b/02-示例报表/最终排名-示例.xlsx
@@ -19,37 +19,37 @@
     <t>姓名</t>
   </si>
   <si>
+    <t>选手07</t>
+  </si>
+  <si>
+    <t>选手03</t>
+  </si>
+  <si>
+    <t>选手08</t>
+  </si>
+  <si>
+    <t>选手04</t>
+  </si>
+  <si>
     <t>选手02</t>
   </si>
   <si>
-    <t>选手03</t>
-  </si>
-  <si>
-    <t>选手08</t>
+    <t>选手09</t>
+  </si>
+  <si>
+    <t>选手06</t>
+  </si>
+  <si>
+    <t>选手01</t>
   </si>
   <si>
     <t>选手10</t>
   </si>
   <si>
-    <t>选手07</t>
-  </si>
-  <si>
-    <t>选手04</t>
-  </si>
-  <si>
     <t>选手05</t>
   </si>
   <si>
-    <t>选手09</t>
-  </si>
-  <si>
-    <t>选手06</t>
-  </si>
-  <si>
-    <t>选手01</t>
-  </si>
-  <si>
-    <t>导出时间：2026-10-17 15:31:57（北京时间）｜导出人：示例数据｜共 10 位选手</t>
+    <t>导出时间：2026-10-17 15:52:20（北京时间）｜导出人：示例数据｜共 10 位选手</t>
   </si>
 </sst>
 </file>
